--- a/estoque_app/template_contagem_inventario.xlsx
+++ b/estoque_app/template_contagem_inventario.xlsx
@@ -1,124 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contagem" sheetId="1" r:id="R787f0d14794b431e"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contagem" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:color rgb="FFFFFFFF"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1F6FEB"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-  <x:colors>
-    <x:indexedColors>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008000"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00808000"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="00C0C0C0"/>
-      <x:rgbColor rgb="00808080"/>
-      <x:rgbColor rgb="009999FF"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00FFFFCC"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00660066"/>
-      <x:rgbColor rgb="00FF8080"/>
-      <x:rgbColor rgb="000066CC"/>
-      <x:rgbColor rgb="00CCCCFF"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="0000CCFF"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00CCFFCC"/>
-      <x:rgbColor rgb="00FFFF99"/>
-      <x:rgbColor rgb="0099CCFF"/>
-      <x:rgbColor rgb="00FF99CC"/>
-      <x:rgbColor rgb="00CC99FF"/>
-      <x:rgbColor rgb="00FFCC99"/>
-      <x:rgbColor rgb="003366FF"/>
-      <x:rgbColor rgb="0033CCCC"/>
-      <x:rgbColor rgb="0099CC00"/>
-      <x:rgbColor rgb="00FFCC00"/>
-      <x:rgbColor rgb="00FF9900"/>
-      <x:rgbColor rgb="00FF6600"/>
-      <x:rgbColor rgb="00666699"/>
-      <x:rgbColor rgb="00969696"/>
-      <x:rgbColor rgb="00003366"/>
-      <x:rgbColor rgb="00339966"/>
-      <x:rgbColor rgb="00003300"/>
-      <x:rgbColor rgb="00333300"/>
-      <x:rgbColor rgb="00993300"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00333399"/>
-      <x:rgbColor rgb="00333333"/>
-    </x:indexedColors>
-  </x:colors>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6FEB"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -164,14 +177,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -227,7 +298,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -236,13 +307,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -276,6 +347,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -330,52 +412,73 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" customWidth="1"/>
-    <x:col min="2" max="2" width="22" customWidth="1"/>
-    <x:col min="3" max="3" width="18" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>COD</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="str">
-        <x:v>UNIDADE_DE_MEDIDA</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="str">
-        <x:v>SALDO_CONTADO</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>PAR-0001</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>UN</x:v>
-      </x:c>
-      <x:c r="C2" t="n">
-        <x:v>124</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>CAB-0012</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>M</x:v>
-      </x:c>
-      <x:c r="C3" t="n">
-        <x:v>78.5</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>UNIDADE_DE_MEDIDA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SALDO_CONTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PAR-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAB-0012</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>